--- a/performance-dashboard/archive/交易表现_20260226.xlsx
+++ b/performance-dashboard/archive/交易表现_20260226.xlsx
@@ -533,26 +533,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,007,955.70</t>
+          <t>¥1,006,745.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+7,955.70</t>
+          <t>¥+6,745.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+24.84%</t>
+          <t>+18.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.494</v>
+        <v>3.413</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,24 +561,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0996%</t>
+          <t>0.0752%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1456%</t>
+          <t>4.9736%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -609,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,414.32</t>
+          <t>¥1,012,319.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,414.32</t>
+          <t>¥+12,319.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+41.26%</t>
+          <t>+36.14%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.984</v>
+        <v>2.766</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1575%</t>
+          <t>0.1390%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12.6378%</t>
+          <t>11.9441%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -685,26 +685,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,867.32</t>
+          <t>¥1,002,904.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,867.32</t>
+          <t>¥+2,904.72</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+7.58%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.387</v>
+        <v>2.672</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,24 +713,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0484%</t>
+          <t>0.0323%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.3272%</t>
+          <t>2.3091%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -761,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,005,355.08</t>
+          <t>¥1,004,162.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+5,355.08</t>
+          <t>¥+4,162.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+16.13%</t>
+          <t>+11.04%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.63</v>
+        <v>2.441</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0671%</t>
+          <t>0.0465%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.1133%</t>
+          <t>3.9872%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -837,52 +837,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,522.76</t>
+          <t>¥1,000,089.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,522.76</t>
+          <t>¥+89.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+10.35%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.918</v>
+        <v>-0.473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0442%</t>
+          <t>0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3.1350%</t>
+          <t>3.5285%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -913,26 +913,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,009,283.84</t>
+          <t>¥1,007,917.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+9,283.84</t>
+          <t>¥+7,917.87</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+29.53%</t>
+          <t>+21.99%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6.053</v>
+        <v>4.567</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -941,24 +941,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.1160%</t>
+          <t>0.0881%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4.5012%</t>
+          <t>4.4251%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -989,26 +989,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,024,989.53</t>
+          <t>¥1,023,966.21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+24,989.53</t>
+          <t>¥+23,966.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+99.59%</t>
+          <t>+81.63%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9.132999999999999</v>
+        <v>7.963</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.3104%</t>
+          <t>0.2648%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8.3470%</t>
+          <t>8.1314%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1065,26 +1065,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,010,819.86</t>
+          <t>¥1,009,096.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+10,819.86</t>
+          <t>¥+9,096.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+35.17%</t>
+          <t>+25.63%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.214</v>
+        <v>3.21</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,24 +1093,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1358%</t>
+          <t>0.1017%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7.6483%</t>
+          <t>7.3709%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1141,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,012,917.46</t>
+          <t>¥1,011,569.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+12,917.46</t>
+          <t>¥+11,569.49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+43.24%</t>
+          <t>+33.63%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10.685</v>
+        <v>8.186</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1169,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1608%</t>
+          <t>0.1282%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.6075%</t>
+          <t>3.7038%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1217,26 +1217,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,022,896.42</t>
+          <t>¥1,020,640.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+22,896.42</t>
+          <t>¥+20,640.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+88.49%</t>
+          <t>+67.34%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9.382</v>
+        <v>7.464</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.2845%</t>
+          <t>0.2284%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.4296%</t>
+          <t>7.4440%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1293,26 +1293,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,008,287.74</t>
+          <t>¥1,006,718.44</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+8,287.74</t>
+          <t>¥+6,718.44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+26.00%</t>
+          <t>+18.38%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.649</v>
+        <v>3.335</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1321,24 +1321,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.1038%</t>
+          <t>0.0749%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5.1978%</t>
+          <t>5.0685%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1369,26 +1369,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,012,215.45</t>
+          <t>¥1,010,687.79</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+12,215.45</t>
+          <t>¥+10,687.79</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+40.49%</t>
+          <t>+30.72%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.996</v>
+        <v>6.133</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1397,24 +1397,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.1523%</t>
+          <t>0.1186%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4.5521%</t>
+          <t>4.5506%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1445,26 +1445,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,014,001.52</t>
+          <t>¥1,015,216.12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+14,001.52</t>
+          <t>¥+15,216.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+47.60%</t>
+          <t>+46.31%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.162000000000001</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1473,24 +1473,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.1745%</t>
+          <t>0.1684%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5.1441%</t>
+          <t>4.8576%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥999,962.00</t>
+          <t>¥999,955.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-38.00</t>
+          <t>¥-44.70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-1353.68</v>
+        <v>-1198.58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.0016%</t>
+          <t>0.0018%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1597,52 +1597,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥1,000,238.51</t>
+          <t>¥999,913.51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥+238.51</t>
+          <t>¥-86.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-10.954</v>
+        <v>-10.779</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0030%</t>
+          <t>-0.0010%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.1122%</t>
+          <t>0.2062%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1673,26 +1673,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥1,004,682.22</t>
+          <t>¥1,006,642.72</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥+4,682.22</t>
+          <t>¥+6,642.72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+13.97%</t>
+          <t>+18.16%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.371</v>
+        <v>3.231</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.0590%</t>
+          <t>0.0741%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5.4340%</t>
+          <t>5.1680%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>¥1,014,807.05</t>
+          <t>¥1,020,166.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>¥+14,807.05</t>
+          <t>¥+20,166.25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+50.92%</t>
+          <t>+65.39%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11.055</v>
+        <v>12.997</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1777,24 +1777,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.1842%</t>
+          <t>0.2224%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4.0201%</t>
+          <t>4.1604%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1825,26 +1825,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>¥1,061,603.19</t>
+          <t>¥1,072,892.19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>¥+61,603.19</t>
+          <t>¥+72,892.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.29%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+433.26%</t>
+          <t>+488.86%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34.323</v>
+        <v>36.466</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.7506%</t>
+          <t>0.7854%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.4535%</t>
+          <t>5.3731%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1901,26 +1901,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>¥1,006,301.78</t>
+          <t>¥1,008,010.58</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>¥+6,301.78</t>
+          <t>¥+8,010.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+19.23%</t>
+          <t>+22.27%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17.793</v>
+        <v>19.438</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1929,24 +1929,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0786%</t>
+          <t>0.0887%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.0015%</t>
+          <t>1.0482%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -1977,26 +1977,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>¥1,061,631.42</t>
+          <t>¥1,075,046.22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>¥+61,631.42</t>
+          <t>¥+75,046.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.50%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+433.66%</t>
+          <t>+519.39%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>28.498</v>
+        <v>30.083</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2005,24 +2005,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.7512%</t>
+          <t>0.8082%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.5736%</t>
+          <t>6.7041%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2053,26 +2053,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>¥1,062,825.52</t>
+          <t>¥1,077,526.32</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>¥+62,825.52</t>
+          <t>¥+77,526.32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.28%</t>
+          <t>+7.75%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+450.73%</t>
+          <t>+556.42%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>24.846</v>
+        <v>26.449</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.7657%</t>
+          <t>0.8343%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7.6864%</t>
+          <t>7.8743%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2225,26 +2225,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,007,955.70</t>
+          <t>¥1,006,745.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+7,955.70</t>
+          <t>¥+6,745.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+24.84%</t>
+          <t>+18.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.494</v>
+        <v>3.413</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2253,24 +2253,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0996%</t>
+          <t>0.0752%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1456%</t>
+          <t>4.9736%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2301,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,414.32</t>
+          <t>¥1,012,319.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,414.32</t>
+          <t>¥+12,319.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+41.26%</t>
+          <t>+36.14%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.984</v>
+        <v>2.766</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2329,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1575%</t>
+          <t>0.1390%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12.6378%</t>
+          <t>11.9441%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,867.32</t>
+          <t>¥1,002,904.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,867.32</t>
+          <t>¥+2,904.72</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+7.58%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.387</v>
+        <v>2.672</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0484%</t>
+          <t>0.0323%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.3272%</t>
+          <t>2.3091%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2453,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,005,355.08</t>
+          <t>¥1,004,162.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+5,355.08</t>
+          <t>¥+4,162.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+16.13%</t>
+          <t>+11.04%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.63</v>
+        <v>2.441</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2481,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0671%</t>
+          <t>0.0465%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.1133%</t>
+          <t>3.9872%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2529,52 +2529,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,003,522.76</t>
+          <t>¥1,000,089.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+3,522.76</t>
+          <t>¥+89.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+10.35%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.918</v>
+        <v>-0.473</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0442%</t>
+          <t>0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3.1350%</t>
+          <t>3.5285%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2701,26 +2701,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,009,283.84</t>
+          <t>¥1,007,917.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+9,283.84</t>
+          <t>¥+7,917.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+29.53%</t>
+          <t>+21.99%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.053</v>
+        <v>4.567</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2729,24 +2729,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1160%</t>
+          <t>0.0881%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.5012%</t>
+          <t>4.4251%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,024,989.53</t>
+          <t>¥1,023,966.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+24,989.53</t>
+          <t>¥+23,966.21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.50%</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+99.59%</t>
+          <t>+81.63%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9.132999999999999</v>
+        <v>7.963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.3104%</t>
+          <t>0.2648%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>8.3470%</t>
+          <t>8.1314%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2853,26 +2853,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,010,819.86</t>
+          <t>¥1,009,096.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+10,819.86</t>
+          <t>¥+9,096.75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+35.17%</t>
+          <t>+25.63%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.214</v>
+        <v>3.21</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2881,24 +2881,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1358%</t>
+          <t>0.1017%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7.6483%</t>
+          <t>7.3709%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -2929,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,012,917.46</t>
+          <t>¥1,011,569.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+12,917.46</t>
+          <t>¥+11,569.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+43.24%</t>
+          <t>+33.63%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.685</v>
+        <v>8.186</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2957,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1608%</t>
+          <t>0.1282%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.6075%</t>
+          <t>3.7038%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3005,26 +3005,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,022,896.42</t>
+          <t>¥1,020,640.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+22,896.42</t>
+          <t>¥+20,640.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+88.49%</t>
+          <t>+67.34%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9.382</v>
+        <v>7.464</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2845%</t>
+          <t>0.2284%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.4296%</t>
+          <t>7.4440%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3177,26 +3177,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,008,287.74</t>
+          <t>¥1,006,718.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+8,287.74</t>
+          <t>¥+6,718.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+26.00%</t>
+          <t>+18.38%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.649</v>
+        <v>3.335</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3205,24 +3205,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1038%</t>
+          <t>0.0749%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1978%</t>
+          <t>5.0685%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3253,26 +3253,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,012,215.45</t>
+          <t>¥1,010,687.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+12,215.45</t>
+          <t>¥+10,687.79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+40.49%</t>
+          <t>+30.72%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.996</v>
+        <v>6.133</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3281,24 +3281,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1523%</t>
+          <t>0.1186%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.5521%</t>
+          <t>4.5506%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3329,26 +3329,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,014,001.52</t>
+          <t>¥1,015,216.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+14,001.52</t>
+          <t>¥+15,216.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.40%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+47.60%</t>
+          <t>+46.31%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.162000000000001</v>
+        <v>8.329000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3357,24 +3357,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1745%</t>
+          <t>0.1684%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.1441%</t>
+          <t>4.8576%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥999,962.00</t>
+          <t>¥999,955.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-38.00</t>
+          <t>¥-44.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1353.68</v>
+        <v>-1198.58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0016%</t>
+          <t>0.0018%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3481,52 +3481,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,000,238.51</t>
+          <t>¥999,913.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+238.51</t>
+          <t>¥-86.49</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-10.954</v>
+        <v>-10.779</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0030%</t>
+          <t>-0.0010%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.1122%</t>
+          <t>0.2062%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,004,682.22</t>
+          <t>¥1,006,642.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+4,682.22</t>
+          <t>¥+6,642.72</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+13.97%</t>
+          <t>+18.16%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.371</v>
+        <v>3.231</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0590%</t>
+          <t>0.0741%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.4340%</t>
+          <t>5.1680%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3825,26 +3825,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,014,807.05</t>
+          <t>¥1,020,166.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+14,807.05</t>
+          <t>¥+20,166.25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+2.02%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+50.92%</t>
+          <t>+65.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11.055</v>
+        <v>12.997</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3853,24 +3853,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1842%</t>
+          <t>0.2224%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4.0201%</t>
+          <t>4.1604%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,061,603.19</t>
+          <t>¥1,072,892.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+61,603.19</t>
+          <t>¥+72,892.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.29%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+433.26%</t>
+          <t>+488.86%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34.323</v>
+        <v>36.466</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3929,24 +3929,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7506%</t>
+          <t>0.7854%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.4535%</t>
+          <t>5.3731%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -3977,26 +3977,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,006,301.78</t>
+          <t>¥1,008,010.58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+6,301.78</t>
+          <t>¥+8,010.58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.80%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+19.23%</t>
+          <t>+22.27%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17.793</v>
+        <v>19.438</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0786%</t>
+          <t>0.0887%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.0015%</t>
+          <t>1.0482%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -4053,26 +4053,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,061,631.42</t>
+          <t>¥1,075,046.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+61,631.42</t>
+          <t>¥+75,046.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+7.50%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+433.66%</t>
+          <t>+519.39%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28.498</v>
+        <v>30.083</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4081,24 +4081,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7512%</t>
+          <t>0.8082%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6.5736%</t>
+          <t>6.7041%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
@@ -4129,26 +4129,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,062,825.52</t>
+          <t>¥1,077,526.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+62,825.52</t>
+          <t>¥+77,526.32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.28%</t>
+          <t>+7.75%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+450.73%</t>
+          <t>+556.42%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>24.846</v>
+        <v>26.449</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4157,24 +4157,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.7657%</t>
+          <t>0.8343%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.6864%</t>
+          <t>7.8743%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260225</t>
+          <t>20260226</t>
         </is>
       </c>
     </row>
